--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendrapisal/reiProjects/product-automation/govgrants-product-automation/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98980FE7-032B-4FE8-8842-C85F691DE542}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C367E1-1965-D149-B927-BFB2644C9121}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="23260" windowHeight="12580" firstSheet="1" activeTab="2" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -67,12 +67,6 @@
     <t>Automation Test Description</t>
   </si>
   <si>
-    <t>Automation Execution Strategic Goal</t>
-  </si>
-  <si>
-    <t>Automation Execution Objective</t>
-  </si>
-  <si>
     <t>Automation Execution Strategic Plan</t>
   </si>
   <si>
@@ -80,6 +74,12 @@
   </si>
   <si>
     <t>fieldStrategyTitle__c</t>
+  </si>
+  <si>
+    <t>Automation Permanent Objective</t>
+  </si>
+  <si>
+    <t>Automation Permanent Strategic Goal</t>
   </si>
 </sst>
 </file>
@@ -445,13 +445,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,7 +462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -470,10 +470,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -484,7 +484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -503,14 +503,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,12 +521,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -541,14 +541,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="34.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,15 +559,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -579,13 +579,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -615,13 +615,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -640,7 +640,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -652,13 +652,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BackWardCompatibility_Project\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EA89C5-7BB0-46CA-9F44-B5E831F828CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C11A22-2C08-49D5-B6A1-F7288812AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="5" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -49,13 +49,7 @@
     <t>None</t>
   </si>
   <si>
-    <t>StrategyTitle__c</t>
-  </si>
-  <si>
     <t>Overview</t>
-  </si>
-  <si>
-    <t>StrategyDescription__c</t>
   </si>
   <si>
     <t>Automation Test Description</t>
@@ -452,13 +446,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,34 +463,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>730</v>
@@ -510,14 +504,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,15 +522,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -548,14 +542,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,15 +560,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -586,13 +580,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,15 +597,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -622,13 +616,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -639,15 +633,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -659,13 +653,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,15 +670,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EA89C5-7BB0-46CA-9F44-B5E831F828CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4C585A-DFB3-4C9A-85BF-A279B229D156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -76,10 +76,10 @@
     <t>Automation Runtime Execution Strategic Plan</t>
   </si>
   <si>
-    <t>fieldStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldEndDate__c</t>
+    <t>StartDate__c</t>
+  </si>
+  <si>
+    <t>EndDate__c</t>
   </si>
 </sst>
 </file>
@@ -452,13 +452,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,18 +469,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -491,7 +491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -510,14 +510,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,7 +528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -548,14 +548,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,7 +566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -586,13 +586,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,7 +603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -622,13 +622,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -639,7 +639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -659,13 +659,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,7 +676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EA89C5-7BB0-46CA-9F44-B5E831F828CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9CA148-B698-47EC-A4DE-131266298768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -67,19 +67,13 @@
     <t>Automation Execution Objective</t>
   </si>
   <si>
-    <t>fieldStrategyDescription__c</t>
-  </si>
-  <si>
-    <t>fieldStrategyTitle__c</t>
-  </si>
-  <si>
     <t>Automation Runtime Execution Strategic Plan</t>
   </si>
   <si>
-    <t>fieldStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldEndDate__c</t>
+    <t>StartDate__c</t>
+  </si>
+  <si>
+    <t>EndDate__c</t>
   </si>
 </sst>
 </file>
@@ -155,9 +149,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -195,7 +189,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -301,7 +295,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -443,7 +437,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -452,13 +446,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,34 +463,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>730</v>
@@ -510,14 +504,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,12 +522,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -548,14 +542,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,12 +560,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -586,13 +580,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,7 +597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -622,13 +616,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -639,7 +633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -659,13 +653,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,7 +670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/StrategicPlan_Field_Values.xlsx
+++ b/src/main/resources/StrategicPlan_Field_Values.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9CA148-B698-47EC-A4DE-131266298768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D8D545-DAF6-471A-B186-7C15328189BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{71FE9D5D-4309-4F80-A035-2E28B4707F3C}"/>
   </bookViews>
   <sheets>
     <sheet name="StrategicPlanCreation" sheetId="1" r:id="rId1"/>
-    <sheet name="StrategicPlanEdition" sheetId="2" r:id="rId2"/>
-    <sheet name="StrategicGoalCreation" sheetId="3" r:id="rId3"/>
-    <sheet name="StrategicGoalEdition" sheetId="4" r:id="rId4"/>
-    <sheet name="ObjectiveCreation" sheetId="5" r:id="rId5"/>
-    <sheet name="ObjectiveEdition" sheetId="6" r:id="rId6"/>
+    <sheet name="Grantee_StrategicPlanCreation" sheetId="7" r:id="rId2"/>
+    <sheet name="StrategicPlanEdition" sheetId="2" r:id="rId3"/>
+    <sheet name="StrategicGoalCreation" sheetId="3" r:id="rId4"/>
+    <sheet name="StrategicGoalEdition" sheetId="4" r:id="rId5"/>
+    <sheet name="ObjectiveCreation" sheetId="5" r:id="rId6"/>
+    <sheet name="ObjectiveEdition" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="13">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -446,13 +447,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9837C433-2C9A-4F7C-97EE-1D5C997FE884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,7 +464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -474,7 +475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -485,7 +486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -502,16 +503,52 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B372FA7F-BFDB-4592-8839-A30E32E1133B}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA57190-D900-451B-810A-BD57BAEC856E}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,7 +559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -539,17 +576,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9653EDE-4E0B-4AC6-BAEF-CF93CD09025C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,7 +597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -577,16 +614,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BB8A33-24B3-4864-BE50-676E7C8A1E49}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -597,7 +634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -613,16 +650,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24210023-6C88-4225-A708-33A47A891615}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -650,16 +687,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02892048-8F2D-4DC2-B040-2F7DFB652348}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -670,7 +707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
